--- a/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS/c. Socialización con la comunidad académica de acciones y avances/F12_Laboratorios_y_Software_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 12. RECURSOS FÍSICOS Y TECNOLÓGICOS/c. Socialización con la comunidad académica de acciones y avances/F12_Laboratorios_y_Software_Profundizacion.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -679,25 +679,49 @@
         <v>4</v>
       </c>
     </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Estudiantes activos Profundización 2022-2026 (únicos)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Activos Profundización en 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="9" t="n">
+        <v>164</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="C6:H6"/>
+  <mergeCells count="21">
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A6:B6"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="C7:H7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C6:H6"/>
     <mergeCell ref="C5:H5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="G10:H10"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="G9:H9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
